--- a/WorkBot/refactor-experimental/data/orders/UNFI/UNFI_Collegetown_20251114.xlsx
+++ b/WorkBot/refactor-experimental/data/orders/UNFI/UNFI_Collegetown_20251114.xlsx
@@ -454,20 +454,14 @@
           <t>Poppi Soda - Doc Pop</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>23.91</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>47.82</t>
-        </is>
+      <c r="C2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.91</v>
+      </c>
+      <c r="E2" t="n">
+        <v>47.82</v>
       </c>
     </row>
     <row r="3">
@@ -481,20 +475,14 @@
           <t>San Pellegrino - Aranciata Rossa (Blood Orange)</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>28.98</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>28.98</t>
-        </is>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>28.98</v>
+      </c>
+      <c r="E3" t="n">
+        <v>28.98</v>
       </c>
     </row>
     <row r="4">
@@ -508,20 +496,14 @@
           <t>San Pellegrino - Aranciata (Orange)</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>28.98</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>28.98</t>
-        </is>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>28.98</v>
+      </c>
+      <c r="E4" t="n">
+        <v>28.98</v>
       </c>
     </row>
     <row r="5">
@@ -535,20 +517,14 @@
           <t>San Pellegrino - Limonata (Lemon)</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>28.98</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>28.98</t>
-        </is>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>28.98</v>
+      </c>
+      <c r="E5" t="n">
+        <v>28.98</v>
       </c>
     </row>
     <row r="6">
@@ -562,20 +538,14 @@
           <t>San Pellegrino - Melograno &amp; Arancia (Pomegranate)</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>28.98</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>28.98</t>
-        </is>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>28.98</v>
+      </c>
+      <c r="E6" t="n">
+        <v>28.98</v>
       </c>
     </row>
     <row r="7">
@@ -589,20 +559,14 @@
           <t>GTS, Kombucha - Gingerade</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>42.02</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>42.02</t>
-        </is>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>42.02</v>
+      </c>
+      <c r="E7" t="n">
+        <v>42.02</v>
       </c>
     </row>
     <row r="8">
@@ -616,20 +580,14 @@
           <t>GTS, Kombucha - Strawberry</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>42.02</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>42.02</t>
-        </is>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>42.02</v>
+      </c>
+      <c r="E8" t="n">
+        <v>42.02</v>
       </c>
     </row>
     <row r="9">
@@ -643,20 +601,14 @@
           <t>Just Tea - Half &amp; Half</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>25.92</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>25.92</t>
-        </is>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>25.92</v>
+      </c>
+      <c r="E9" t="n">
+        <v>25.92</v>
       </c>
     </row>
     <row r="10">
@@ -670,20 +622,14 @@
           <t>So Good So You - Detox Pineapple</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>37.62</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>75.24</t>
-        </is>
+      <c r="C10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" t="n">
+        <v>37.62</v>
+      </c>
+      <c r="E10" t="n">
+        <v>75.23999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -697,20 +643,14 @@
           <t>So Good So You - Immunity Watermelon</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>37.62</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>75.24</t>
-        </is>
+      <c r="C11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" t="n">
+        <v>37.62</v>
+      </c>
+      <c r="E11" t="n">
+        <v>75.23999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -724,20 +664,14 @@
           <t>Martinelli's Apple Juice Squat</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>43.85</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>43.85</t>
-        </is>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>43.85</v>
+      </c>
+      <c r="E12" t="n">
+        <v>43.85</v>
       </c>
     </row>
     <row r="13">
@@ -751,20 +685,14 @@
           <t>Remedy - Superseed Fuel</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>35.00</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>70.00</t>
-        </is>
+      <c r="C13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" t="n">
+        <v>35</v>
+      </c>
+      <c r="E13" t="n">
+        <v>70</v>
       </c>
     </row>
     <row r="14">
@@ -778,20 +706,14 @@
           <t>Remedy - Matcha Fuel</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>25.06</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>25.06</t>
-        </is>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="n">
+        <v>25.06</v>
+      </c>
+      <c r="E14" t="n">
+        <v>25.06</v>
       </c>
     </row>
     <row r="15">
@@ -805,20 +727,14 @@
           <t>Suji - Tumeric Love</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>22.99</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>45.98</t>
-        </is>
+      <c r="C15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" t="n">
+        <v>22.99</v>
+      </c>
+      <c r="E15" t="n">
+        <v>45.98</v>
       </c>
     </row>
     <row r="16">
@@ -832,20 +748,14 @@
           <t>Suja - Green Delight</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>22.99</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>45.98</t>
-        </is>
+      <c r="C16" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" t="n">
+        <v>22.99</v>
+      </c>
+      <c r="E16" t="n">
+        <v>45.98</v>
       </c>
     </row>
     <row r="17">
@@ -859,20 +769,14 @@
           <t>Suja - Fruit Drink</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>22.99</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>45.98</t>
-        </is>
+      <c r="C17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" t="n">
+        <v>22.99</v>
+      </c>
+      <c r="E17" t="n">
+        <v>45.98</v>
       </c>
     </row>
   </sheetData>
